--- a/InputData/dist-heat/BFoHPbF/BAU Frac of Heat Provided by Fuel.xlsx
+++ b/InputData/dist-heat/BFoHPbF/BAU Frac of Heat Provided by Fuel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26216"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0f0dd5cd5bd3d87a/Documents/IESR/Data Statistik/EPS Data/NEW/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/dist-heat/BFoHPbF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{54263B1F-4804-432C-9849-66BD0A8B2C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1ED6FCBC-990D-4902-B536-DB3288C72189}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDE9EB9-E4A1-7242-BBDF-70D8ED7DC48A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -241,9 +241,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -281,9 +281,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -316,26 +316,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -368,26 +351,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -562,17 +528,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="58.1328125" customWidth="1"/>
+    <col min="2" max="2" width="58.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -580,72 +546,72 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B4" s="2">
         <v>2014</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -662,15 +628,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.3984375" customWidth="1"/>
-    <col min="2" max="2" width="19.3984375" customWidth="1"/>
-    <col min="3" max="3" width="17.3984375" customWidth="1"/>
-    <col min="4" max="4" width="12.3984375" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>14</v>
       </c>
@@ -682,7 +648,7 @@
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B2">
         <v>2000</v>
       </c>
@@ -705,7 +671,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -731,7 +697,7 @@
         <v>8544</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -757,7 +723,7 @@
         <v>12343.4</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -783,7 +749,7 @@
         <v>199.7</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -809,7 +775,7 @@
         <v>4055.7</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -835,7 +801,7 @@
         <v>2641.4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B9" s="5" t="s">
         <v>16</v>
       </c>
@@ -846,7 +812,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -863,7 +829,7 @@
         <v>0.63892242256425869</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -880,7 +846,7 @@
         <v>0.17030120384160674</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -897,7 +863,7 @@
         <v>3.3910556428748871E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -914,7 +880,7 @@
         <v>0.15686581716538556</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -937,14 +903,14 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AK11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:BE11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.1328125" customWidth="1"/>
-    <col min="2" max="2" width="9.3984375" customWidth="1"/>
+    <col min="1" max="1" width="24.1640625" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:57" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
         <v>32</v>
       </c>
@@ -1056,8 +1022,68 @@
       <c r="AK1">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="AL1">
+        <v>2051</v>
+      </c>
+      <c r="AM1">
+        <v>2052</v>
+      </c>
+      <c r="AN1">
+        <v>2053</v>
+      </c>
+      <c r="AO1">
+        <v>2054</v>
+      </c>
+      <c r="AP1">
+        <v>2055</v>
+      </c>
+      <c r="AQ1">
+        <v>2056</v>
+      </c>
+      <c r="AR1">
+        <v>2057</v>
+      </c>
+      <c r="AS1">
+        <v>2058</v>
+      </c>
+      <c r="AT1">
+        <v>2059</v>
+      </c>
+      <c r="AU1">
+        <v>2060</v>
+      </c>
+      <c r="AV1">
+        <v>2061</v>
+      </c>
+      <c r="AW1">
+        <v>2062</v>
+      </c>
+      <c r="AX1">
+        <v>2063</v>
+      </c>
+      <c r="AY1">
+        <v>2064</v>
+      </c>
+      <c r="AZ1">
+        <v>2065</v>
+      </c>
+      <c r="BA1">
+        <v>2066</v>
+      </c>
+      <c r="BB1">
+        <v>2067</v>
+      </c>
+      <c r="BC1">
+        <v>2068</v>
+      </c>
+      <c r="BD1">
+        <v>2069</v>
+      </c>
+      <c r="BE1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1069,7 +1095,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="10">
-        <f t="shared" ref="D2:AK7" si="0">$B2</f>
+        <f t="shared" ref="D2:AL7" si="0">$B2</f>
         <v>0</v>
       </c>
       <c r="E2" s="10">
@@ -1204,8 +1230,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="AL2" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM2" s="10">
+        <f t="shared" ref="AL2:BE11" si="1">$B2</f>
+        <v>0</v>
+      </c>
+      <c r="AN2" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO2" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP2" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR2" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS2" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT2" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU2" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV2" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW2" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX2" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY2" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA2" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB2" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BC2" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BD2" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BE2" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1317,8 +1423,68 @@
       <c r="AK3" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="AL3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA3" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB3" s="10">
+        <v>0</v>
+      </c>
+      <c r="BC3" s="10">
+        <v>0</v>
+      </c>
+      <c r="BD3" s="10">
+        <v>0</v>
+      </c>
+      <c r="BE3" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1430,8 +1596,68 @@
       <c r="AK4" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="AL4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA4" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB4" s="10">
+        <v>0</v>
+      </c>
+      <c r="BC4" s="10">
+        <v>0</v>
+      </c>
+      <c r="BD4" s="10">
+        <v>0</v>
+      </c>
+      <c r="BE4" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1543,8 +1769,68 @@
       <c r="AK5" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="AL5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB5" s="10">
+        <v>0</v>
+      </c>
+      <c r="BC5" s="10">
+        <v>0</v>
+      </c>
+      <c r="BD5" s="10">
+        <v>0</v>
+      </c>
+      <c r="BE5" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1656,8 +1942,68 @@
       <c r="AK6" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="AL6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB6" s="10">
+        <v>0</v>
+      </c>
+      <c r="BC6" s="10">
+        <v>0</v>
+      </c>
+      <c r="BD6" s="10">
+        <v>0</v>
+      </c>
+      <c r="BE6" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1665,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="10">
-        <f t="shared" ref="C3:R11" si="1">$B7</f>
+        <f t="shared" ref="C7:R11" si="2">$B7</f>
         <v>0</v>
       </c>
       <c r="D7" s="10">
@@ -1804,8 +2150,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="AL7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BC7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BD7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BE7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1813,147 +2239,227 @@
         <v>0</v>
       </c>
       <c r="C8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S8" s="10">
-        <f t="shared" ref="S8:AH11" si="2">$B8</f>
+        <f t="shared" ref="S8:AH11" si="3">$B8</f>
         <v>0</v>
       </c>
       <c r="T8" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U8" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V8" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W8" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X8" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y8" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z8" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA8" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB8" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC8" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD8" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE8" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF8" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG8" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH8" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI8" s="10">
-        <f t="shared" ref="AI8:AK11" si="3">$B8</f>
+        <f t="shared" ref="AI8:AX11" si="4">$B8</f>
         <v>0</v>
       </c>
       <c r="AJ8" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AK8" s="10">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AL8" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AM8" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AN8" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AO8" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AP8" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AR8" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AS8" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AT8" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AU8" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AV8" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AW8" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AX8" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AY8" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA8" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB8" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BC8" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BD8" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BE8" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1961,147 +2467,227 @@
         <v>0</v>
       </c>
       <c r="C9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S9" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T9" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U9" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V9" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W9" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X9" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y9" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z9" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA9" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB9" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC9" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD9" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE9" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF9" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG9" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH9" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI9" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AJ9" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AK9" s="10">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AL9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BC9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BD9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BE9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -2109,147 +2695,227 @@
         <v>0</v>
       </c>
       <c r="C10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S10" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T10" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U10" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V10" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W10" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X10" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y10" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z10" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA10" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB10" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC10" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD10" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE10" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF10" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG10" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH10" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI10" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AJ10" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AK10" s="10">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AL10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BC10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BD10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BE10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2257,143 +2923,223 @@
         <v>0</v>
       </c>
       <c r="C11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI11" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AJ11" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AK11" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AL11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BC11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BD11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BE11" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
